--- a/zabbix_api.xlsx
+++ b/zabbix_api.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="8580" firstSheet="6" activeTab="9"/>
+    <workbookView windowWidth="24000" windowHeight="9675" firstSheet="6" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="01_创建主机组" sheetId="8" r:id="rId1"/>
@@ -2079,7 +2079,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4098290" cy="1291590"/>
+    <xdr:ext cx="4098290" cy="1331595"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -2087,8 +2087,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4236720" y="7620"/>
-          <a:ext cx="4098290" cy="1291590"/>
+          <a:off x="4707255" y="7620"/>
+          <a:ext cx="4098290" cy="1331595"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2226,7 +2226,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>76835</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="927754" cy="2578612"/>
+    <xdr:ext cx="927754" cy="2483362"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -2234,8 +2234,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20506055" y="76835"/>
-          <a:ext cx="927735" cy="2578100"/>
+          <a:off x="22762845" y="76835"/>
+          <a:ext cx="927735" cy="2482850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2386,7 +2386,7 @@
       <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1374607" cy="2403000"/>
+    <xdr:ext cx="1374607" cy="2477295"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="28" name="文本框 27"/>
@@ -2394,8 +2394,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="24629745" y="10515600"/>
-          <a:ext cx="1374140" cy="2402840"/>
+          <a:off x="27366595" y="10677525"/>
+          <a:ext cx="1374140" cy="2477135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2542,7 +2542,7 @@
       <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1656736" cy="2403000"/>
+    <xdr:ext cx="1656736" cy="2477295"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="29" name="文本框 28"/>
@@ -2550,8 +2550,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22778085" y="10515600"/>
-          <a:ext cx="1656715" cy="2402840"/>
+          <a:off x="25309195" y="10677525"/>
+          <a:ext cx="1656715" cy="2477135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2764,7 +2764,7 @@
       <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1684757" cy="1886320"/>
+    <xdr:ext cx="1684757" cy="1943470"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="30" name="文本框 29"/>
@@ -2772,8 +2772,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20926425" y="10515600"/>
-          <a:ext cx="1684655" cy="1885950"/>
+          <a:off x="23251795" y="10677525"/>
+          <a:ext cx="1684655" cy="1943100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2887,7 +2887,7 @@
       <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1239378" cy="1867469"/>
+    <xdr:ext cx="1239378" cy="1924619"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="31" name="文本框 30"/>
@@ -2895,8 +2895,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19691985" y="10515600"/>
-          <a:ext cx="1238885" cy="1866900"/>
+          <a:off x="21880195" y="10677525"/>
+          <a:ext cx="1238885" cy="1924050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3032,7 +3032,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5231130" cy="3068955"/>
+    <xdr:ext cx="5231130" cy="2985135"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="32" name="文本框 31"/>
@@ -3040,8 +3040,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21543645" y="9525"/>
-          <a:ext cx="5231130" cy="3068955"/>
+          <a:off x="23937595" y="9525"/>
+          <a:ext cx="5231130" cy="2985135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3299,7 +3299,7 @@
       <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1252331" cy="1698927"/>
+    <xdr:ext cx="1252331" cy="1750362"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="11" name="文本框 10"/>
@@ -3307,8 +3307,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19691985" y="11567160"/>
-          <a:ext cx="1252220" cy="1698625"/>
+          <a:off x="21880195" y="11763375"/>
+          <a:ext cx="1252220" cy="1750060"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3564,7 +3564,7 @@
       <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1186415" cy="1354473"/>
+    <xdr:ext cx="1186415" cy="1394478"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="12" name="文本框 11"/>
@@ -3572,8 +3572,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20926425" y="11567160"/>
-          <a:ext cx="1186180" cy="1354455"/>
+          <a:off x="23251795" y="11763375"/>
+          <a:ext cx="1186180" cy="1394460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3792,6 +3792,230 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1365885" cy="1918335"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="文本框 1"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22785070" y="1371600"/>
+          <a:ext cx="1365885" cy="1918335"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>IPMI 认证算法。</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>Possible values:</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>-1 - (default) default;</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>0 - none;</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>1 - MD2;</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>2 - MD5</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>4 - straight;</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>5 - OEM;</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>6 - RMCP+.</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1174750" cy="1553210"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="文本框 3"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24547195" y="1666875"/>
+          <a:ext cx="1174750" cy="1553210"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>IPMI 权限级别。</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>Possible values:</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>1 - callback;</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>2 - (default) user;</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>3 - operator;</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>4 - admin;</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>5 - OEM.</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3804,7 +4028,7 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1238885" cy="1310640"/>
+    <xdr:ext cx="1238885" cy="1350645"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -3812,8 +4036,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8411845" y="1927860"/>
-          <a:ext cx="1238885" cy="1310640"/>
+          <a:off x="9345295" y="1990725"/>
+          <a:ext cx="1238885" cy="1350645"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3947,7 +4171,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>635</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="927754" cy="1182247"/>
+    <xdr:ext cx="927754" cy="1216537"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="文本框 3"/>
@@ -3955,8 +4179,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9387205" y="635"/>
-          <a:ext cx="927735" cy="1181735"/>
+          <a:off x="10409555" y="635"/>
+          <a:ext cx="927735" cy="1216025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4107,7 +4331,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4777105" cy="1598295"/>
+    <xdr:ext cx="4777105" cy="1649730"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="5" name="文本框 4"/>
@@ -4115,8 +4339,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10446385" y="9525"/>
-          <a:ext cx="4777105" cy="1598295"/>
+          <a:off x="11605895" y="9525"/>
+          <a:ext cx="4777105" cy="1649730"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4355,7 +4579,7 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1684655" cy="1291590"/>
+    <xdr:ext cx="1684655" cy="1331595"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="8" name="文本框 7"/>
@@ -4363,8 +4587,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9829165" y="1927860"/>
-          <a:ext cx="1684655" cy="1291590"/>
+          <a:off x="10920095" y="1990725"/>
+          <a:ext cx="1684655" cy="1331595"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4476,7 +4700,7 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1656715" cy="1800225"/>
+    <xdr:ext cx="1656715" cy="1857375"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="9" name="文本框 8"/>
@@ -4484,8 +4708,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11680825" y="1927860"/>
-          <a:ext cx="1656715" cy="1800225"/>
+          <a:off x="12977495" y="1990725"/>
+          <a:ext cx="1656715" cy="1857375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4696,7 +4920,7 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1374140" cy="1952625"/>
+    <xdr:ext cx="1374140" cy="2015490"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="10" name="文本框 9"/>
@@ -4704,8 +4928,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13532485" y="1927860"/>
-          <a:ext cx="1374140" cy="1952625"/>
+          <a:off x="15034895" y="1990725"/>
+          <a:ext cx="1374140" cy="2015490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4855,7 +5079,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6116955" cy="2058035"/>
+    <xdr:ext cx="6116955" cy="2120900"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -4863,8 +5087,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5280025" y="9525"/>
-          <a:ext cx="6116955" cy="2058035"/>
+          <a:off x="5866765" y="9525"/>
+          <a:ext cx="6116955" cy="2120900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5146,7 +5370,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6424295" cy="1732915"/>
+    <xdr:ext cx="6424295" cy="1784350"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -5154,8 +5378,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4282440" y="9525"/>
-          <a:ext cx="6424295" cy="1732915"/>
+          <a:off x="4758055" y="9525"/>
+          <a:ext cx="6424295" cy="1784350"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5351,7 +5575,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>50165</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1877437" cy="1624767"/>
+    <xdr:ext cx="1877437" cy="1676202"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="文本框 3"/>
@@ -5359,8 +5583,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6758305" y="225425"/>
-          <a:ext cx="1877060" cy="1624330"/>
+          <a:off x="7498715" y="231140"/>
+          <a:ext cx="1877060" cy="1675765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5589,7 +5813,7 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>26670</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4756785" cy="652145"/>
+    <xdr:ext cx="4756785" cy="669290"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="6" name="文本框 5"/>
@@ -5597,8 +5821,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8930005" y="3181350"/>
-          <a:ext cx="4756785" cy="652145"/>
+          <a:off x="9900920" y="3284220"/>
+          <a:ext cx="4756785" cy="669290"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5699,7 +5923,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1877437" cy="1630482"/>
+    <xdr:ext cx="1877437" cy="1681917"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -5707,8 +5931,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9192260" y="0"/>
-          <a:ext cx="1877060" cy="1630045"/>
+          <a:off x="10213340" y="0"/>
+          <a:ext cx="1877060" cy="1681480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5937,7 +6161,7 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6368415" cy="1389380"/>
+    <xdr:ext cx="6368415" cy="1435100"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="文本框 3"/>
@@ -5945,8 +6169,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6765290" y="1676400"/>
-          <a:ext cx="6368415" cy="1389380"/>
+          <a:off x="7495540" y="1727835"/>
+          <a:ext cx="6368415" cy="1435100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6054,7 +6278,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7948930" cy="989330"/>
+    <xdr:ext cx="7948930" cy="1017905"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -6062,8 +6286,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3916680" y="9525"/>
-          <a:ext cx="7948930" cy="989330"/>
+          <a:off x="4351655" y="9525"/>
+          <a:ext cx="7948930" cy="1017905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6171,7 +6395,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1489831" cy="1630482"/>
+    <xdr:ext cx="1489831" cy="1681917"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -6179,8 +6403,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5020945" y="0"/>
-          <a:ext cx="1489710" cy="1630045"/>
+          <a:off x="5579110" y="0"/>
+          <a:ext cx="1489710" cy="1681480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6405,7 +6629,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2588895" cy="799465"/>
+    <xdr:ext cx="2588895" cy="822325"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="文本框 3"/>
@@ -6413,8 +6637,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8107045" y="9525"/>
-          <a:ext cx="2588895" cy="799465"/>
+          <a:off x="9008110" y="9525"/>
+          <a:ext cx="2588895" cy="822325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6623,7 +6847,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1877437" cy="2029273"/>
+    <xdr:ext cx="1877437" cy="2143573"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -6631,8 +6855,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10610850" y="0"/>
-          <a:ext cx="1877060" cy="2028825"/>
+          <a:off x="11790680" y="0"/>
+          <a:ext cx="1877060" cy="2143125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6885,7 +7109,7 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>48260</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2582758" cy="1170817"/>
+    <xdr:ext cx="2582758" cy="1239397"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="8" name="文本框 7"/>
@@ -6893,8 +7117,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10630535" y="1633220"/>
-          <a:ext cx="2582545" cy="1170305"/>
+          <a:off x="11810365" y="1724660"/>
+          <a:ext cx="2582545" cy="1238885"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7074,7 +7298,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2300605" cy="999490"/>
+    <xdr:ext cx="2300605" cy="1028065"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="文本框 3"/>
@@ -7082,8 +7306,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6172200" y="7620"/>
-          <a:ext cx="2300605" cy="999490"/>
+          <a:off x="6858000" y="7620"/>
+          <a:ext cx="2300605" cy="1028065"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7223,7 +7447,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5208905" cy="1985645"/>
+    <xdr:ext cx="5208905" cy="2048510"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="文本框 3"/>
@@ -7231,8 +7455,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4305300" y="7620"/>
-          <a:ext cx="5208905" cy="1985645"/>
+          <a:off x="4783455" y="7620"/>
+          <a:ext cx="5208905" cy="2048510"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7546,7 +7770,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1270</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1998980" cy="456565"/>
+    <xdr:ext cx="1998980" cy="467995"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -7554,8 +7778,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6323965" y="1270"/>
-          <a:ext cx="1998980" cy="456565"/>
+          <a:off x="7026910" y="1270"/>
+          <a:ext cx="1998980" cy="467995"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7671,7 +7895,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>2540</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2278380" cy="822325"/>
+    <xdr:ext cx="2278380" cy="845185"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -7679,8 +7903,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6172200" y="2540"/>
-          <a:ext cx="2278380" cy="822325"/>
+          <a:off x="6858000" y="2540"/>
+          <a:ext cx="2278380" cy="845185"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7822,7 +8046,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1270</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1998980" cy="456565"/>
+    <xdr:ext cx="1998980" cy="467995"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -7830,8 +8054,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7421245" y="1270"/>
-          <a:ext cx="1998980" cy="456565"/>
+          <a:off x="8246110" y="1270"/>
+          <a:ext cx="1998980" cy="467995"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7947,7 +8171,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>2540</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2138680" cy="822325"/>
+    <xdr:ext cx="2138680" cy="845185"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -7955,8 +8179,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6172200" y="2540"/>
-          <a:ext cx="2138680" cy="822325"/>
+          <a:off x="6858000" y="2540"/>
+          <a:ext cx="2138680" cy="845185"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8098,7 +8322,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1270</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2278380" cy="456565"/>
+    <xdr:ext cx="2278380" cy="467995"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -8106,8 +8330,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6323965" y="1270"/>
-          <a:ext cx="2278380" cy="456565"/>
+          <a:off x="7026910" y="1270"/>
+          <a:ext cx="2278380" cy="467995"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8247,7 +8471,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>2540</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2557780" cy="822325"/>
+    <xdr:ext cx="2557780" cy="845185"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -8255,8 +8479,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6172200" y="2540"/>
-          <a:ext cx="2557780" cy="822325"/>
+          <a:off x="6858000" y="2540"/>
+          <a:ext cx="2557780" cy="845185"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8398,7 +8622,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1270</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2278380" cy="456565"/>
+    <xdr:ext cx="2278380" cy="467995"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -8406,8 +8630,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6323965" y="1270"/>
-          <a:ext cx="2278380" cy="456565"/>
+          <a:off x="7026910" y="1270"/>
+          <a:ext cx="2278380" cy="467995"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8547,7 +8771,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>2540</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2557780" cy="822325"/>
+    <xdr:ext cx="2557780" cy="845185"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -8555,8 +8779,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6172200" y="2540"/>
-          <a:ext cx="2557780" cy="822325"/>
+          <a:off x="6858000" y="2540"/>
+          <a:ext cx="2557780" cy="845185"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8698,7 +8922,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1270</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2278380" cy="456565"/>
+    <xdr:ext cx="2278380" cy="467995"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -8706,8 +8930,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7421245" y="1270"/>
-          <a:ext cx="2278380" cy="456565"/>
+          <a:off x="8246110" y="1270"/>
+          <a:ext cx="2278380" cy="467995"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8823,7 +9047,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>2540</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2418080" cy="822325"/>
+    <xdr:ext cx="2418080" cy="845185"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -8831,8 +9055,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6172200" y="2540"/>
-          <a:ext cx="2418080" cy="822325"/>
+          <a:off x="6858000" y="2540"/>
+          <a:ext cx="2418080" cy="845185"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8974,7 +9198,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1454150" cy="474345"/>
+    <xdr:ext cx="1454150" cy="485775"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -8982,8 +9206,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4458335" y="0"/>
-          <a:ext cx="1454150" cy="474345"/>
+          <a:off x="4954270" y="0"/>
+          <a:ext cx="1454150" cy="485775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9157,7 +9381,7 @@
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5233035" cy="1111885"/>
+    <xdr:ext cx="5233035" cy="1146175"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="文本框 3"/>
@@ -9165,8 +9389,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4458335" y="525780"/>
-          <a:ext cx="5233035" cy="1111885"/>
+          <a:off x="4954270" y="542925"/>
+          <a:ext cx="5233035" cy="1146175"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9450,7 +9674,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1270</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2557780" cy="456565"/>
+    <xdr:ext cx="2557780" cy="467995"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -9458,8 +9682,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6323965" y="1270"/>
-          <a:ext cx="2557780" cy="456565"/>
+          <a:off x="7026910" y="1270"/>
+          <a:ext cx="2557780" cy="467995"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9599,7 +9823,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1905</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1621790" cy="3380740"/>
+    <xdr:ext cx="1621790" cy="3489325"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -9607,8 +9831,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6804025" y="1905"/>
-          <a:ext cx="1621790" cy="3380740"/>
+          <a:off x="7559675" y="1905"/>
+          <a:ext cx="1621790" cy="3489325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9865,7 +10089,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3157855" cy="799465"/>
+    <xdr:ext cx="3157855" cy="822325"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -9873,8 +10097,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8655685" y="9525"/>
-          <a:ext cx="3157855" cy="799465"/>
+          <a:off x="9617075" y="9525"/>
+          <a:ext cx="3157855" cy="822325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10152,7 +10376,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3307316" cy="3913892"/>
+    <xdr:ext cx="3307316" cy="4039622"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -10160,8 +10384,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9552940" y="0"/>
-          <a:ext cx="3307080" cy="3913505"/>
+          <a:off x="10615295" y="0"/>
+          <a:ext cx="3307080" cy="4039235"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10766,7 +10990,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2260427" cy="1429879"/>
+    <xdr:ext cx="2260427" cy="1475599"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -10774,8 +10998,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12639040" y="0"/>
-          <a:ext cx="2259965" cy="1429385"/>
+          <a:off x="14044295" y="0"/>
+          <a:ext cx="2259965" cy="1475105"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11015,7 +11239,7 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2677795" cy="799465"/>
+    <xdr:ext cx="2677795" cy="822325"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="文本框 3"/>
@@ -11023,8 +11247,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12639040" y="2278380"/>
-          <a:ext cx="2677795" cy="799465"/>
+          <a:off x="14044295" y="2352675"/>
+          <a:ext cx="2677795" cy="822325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11352,7 +11576,7 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3256276" cy="474489"/>
+    <xdr:ext cx="3256276" cy="485919"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="5" name="文本框 4"/>
@@ -11360,8 +11584,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12639040" y="1577340"/>
-          <a:ext cx="3255645" cy="474345"/>
+          <a:off x="14044295" y="1628775"/>
+          <a:ext cx="3255645" cy="485775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11635,7 +11859,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1489831" cy="1630482"/>
+    <xdr:ext cx="1489831" cy="1681917"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -11643,8 +11867,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7589520" y="0"/>
-          <a:ext cx="1489710" cy="1630045"/>
+          <a:off x="8432165" y="0"/>
+          <a:ext cx="1489710" cy="1681480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12103,7 +12327,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2600325" cy="799465"/>
+    <xdr:ext cx="2600325" cy="822325"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -12111,8 +12335,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9441180" y="9525"/>
-          <a:ext cx="2600325" cy="799465"/>
+          <a:off x="10489565" y="9525"/>
+          <a:ext cx="2600325" cy="822325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12356,7 +12580,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5986145" cy="1244600"/>
+    <xdr:ext cx="5986145" cy="1284605"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -12364,8 +12588,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9150350" y="9525"/>
-          <a:ext cx="5986145" cy="1244600"/>
+          <a:off x="10167620" y="9525"/>
+          <a:ext cx="5986145" cy="1284605"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12525,7 +12749,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1489831" cy="1630482"/>
+    <xdr:ext cx="1489831" cy="1681917"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -12533,8 +12757,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5020945" y="0"/>
-          <a:ext cx="1489710" cy="1630045"/>
+          <a:off x="5579110" y="0"/>
+          <a:ext cx="1489710" cy="1681480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12857,7 +13081,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1313180" cy="665567"/>
+    <xdr:ext cx="1313180" cy="682712"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -12865,8 +13089,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8107045" y="0"/>
-          <a:ext cx="1313180" cy="665480"/>
+          <a:off x="9008110" y="0"/>
+          <a:ext cx="1313180" cy="682625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -13157,7 +13381,7 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6368415" cy="1389380"/>
+    <xdr:ext cx="6368415" cy="1435100"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -13165,8 +13389,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6765290" y="1676400"/>
-          <a:ext cx="6368415" cy="1389380"/>
+          <a:off x="7495540" y="1727835"/>
+          <a:ext cx="6368415" cy="1435100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -13372,7 +13596,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6368415" cy="1395095"/>
+    <xdr:ext cx="6368415" cy="1435100"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -13380,8 +13604,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4320540" y="175260"/>
-          <a:ext cx="6368415" cy="1395095"/>
+          <a:off x="4800600" y="180975"/>
+          <a:ext cx="6368415" cy="1435100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -13605,7 +13829,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4098290" cy="1291590"/>
+    <xdr:ext cx="4098290" cy="1331595"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -13613,8 +13837,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4794250" y="7620"/>
-          <a:ext cx="4098290" cy="1291590"/>
+          <a:off x="5327015" y="7620"/>
+          <a:ext cx="4098290" cy="1331595"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -13906,7 +14130,7 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3768725" cy="975995"/>
+    <xdr:ext cx="3768725" cy="1004570"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -13914,8 +14138,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4822825" y="1236345"/>
-          <a:ext cx="3768725" cy="975995"/>
+          <a:off x="5355590" y="1276350"/>
+          <a:ext cx="3768725" cy="1004570"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14016,7 +14240,7 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2278380" cy="793750"/>
+    <xdr:ext cx="2278380" cy="822325"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="文本框 3"/>
@@ -14024,8 +14248,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4984750" y="2449830"/>
-          <a:ext cx="2278380" cy="793750"/>
+          <a:off x="5517515" y="2524125"/>
+          <a:ext cx="2278380" cy="822325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14097,7 +14321,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>93980</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4098290" cy="1291590"/>
+    <xdr:ext cx="4098290" cy="1331595"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -14105,8 +14329,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10380980" y="269240"/>
-          <a:ext cx="4098290" cy="1291590"/>
+          <a:off x="11509375" y="274955"/>
+          <a:ext cx="4098290" cy="1331595"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14376,7 +14600,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2778125" cy="799465"/>
+    <xdr:ext cx="2778125" cy="822325"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="9" name="文本框 8"/>
@@ -14384,8 +14608,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7683500" y="175260"/>
-          <a:ext cx="2778125" cy="799465"/>
+          <a:off x="8537575" y="180975"/>
+          <a:ext cx="2778125" cy="822325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14559,7 +14783,7 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2700020" cy="1153160"/>
+    <xdr:ext cx="2700020" cy="1187450"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="14" name="文本框 13"/>
@@ -14567,8 +14791,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7683500" y="1051560"/>
-          <a:ext cx="2700020" cy="1153160"/>
+          <a:off x="8537575" y="1085850"/>
+          <a:ext cx="2700020" cy="1187450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14766,7 +14990,7 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1235075" cy="1153160"/>
+    <xdr:ext cx="1235075" cy="1187450"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="17" name="文本框 16"/>
@@ -14774,8 +14998,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7683500" y="2278380"/>
-          <a:ext cx="1235075" cy="1153160"/>
+          <a:off x="8537575" y="2352675"/>
+          <a:ext cx="1235075" cy="1187450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14957,7 +15181,7 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2827020" cy="799465"/>
+    <xdr:ext cx="2827020" cy="822325"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="18" name="文本框 17"/>
@@ -14965,8 +15189,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7683500" y="3505200"/>
-          <a:ext cx="2827020" cy="799465"/>
+          <a:off x="8537575" y="3619500"/>
+          <a:ext cx="2827020" cy="822325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15132,7 +15356,7 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3106420" cy="975995"/>
+    <xdr:ext cx="3106420" cy="1004570"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="19" name="文本框 18"/>
@@ -15140,8 +15364,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7683500" y="4381500"/>
-          <a:ext cx="3106420" cy="975995"/>
+          <a:off x="8537575" y="4524375"/>
+          <a:ext cx="3106420" cy="1004570"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15315,7 +15539,7 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4809490" cy="975995"/>
+    <xdr:ext cx="4809490" cy="1004570"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="21" name="文本框 20"/>
@@ -15323,8 +15547,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10769600" y="3505200"/>
-          <a:ext cx="4809490" cy="975995"/>
+          <a:off x="11966575" y="3619500"/>
+          <a:ext cx="4809490" cy="1004570"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15494,7 +15718,7 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1894840" cy="1147445"/>
+    <xdr:ext cx="1894840" cy="1187450"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="22" name="文本框 21"/>
@@ -15502,8 +15726,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10428605" y="1535430"/>
-          <a:ext cx="1894840" cy="1147445"/>
+          <a:off x="11557000" y="1581150"/>
+          <a:ext cx="1894840" cy="1187450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15651,7 +15875,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5438140" cy="1888490"/>
+    <xdr:ext cx="5438140" cy="1945640"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -15659,8 +15883,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4263390" y="7620"/>
-          <a:ext cx="5438140" cy="1888490"/>
+          <a:off x="4737100" y="7620"/>
+          <a:ext cx="5438140" cy="1945640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15933,7 +16157,7 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4098290" cy="1291590"/>
+    <xdr:ext cx="4098290" cy="1331595"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -15941,8 +16165,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3703320" y="350520"/>
-          <a:ext cx="4098290" cy="1291590"/>
+          <a:off x="4114800" y="361950"/>
+          <a:ext cx="4098290" cy="1331595"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -16116,7 +16340,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4098290" cy="1291590"/>
+    <xdr:ext cx="4098290" cy="1331595"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -16124,8 +16348,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4236720" y="7620"/>
-          <a:ext cx="4098290" cy="1291590"/>
+          <a:off x="4707255" y="7620"/>
+          <a:ext cx="4098290" cy="1331595"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -16356,7 +16580,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4221480" cy="1137920"/>
+    <xdr:ext cx="4221480" cy="1172210"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -16364,8 +16588,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3989070" y="7620"/>
-          <a:ext cx="4221480" cy="1137920"/>
+          <a:off x="4432300" y="7620"/>
+          <a:ext cx="4221480" cy="1172210"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -16533,7 +16757,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3307316" cy="3913892"/>
+    <xdr:ext cx="3307316" cy="4039622"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="8" name="文本框 7"/>
@@ -16541,8 +16765,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8350885" y="0"/>
-          <a:ext cx="3307080" cy="3913505"/>
+          <a:off x="9279255" y="0"/>
+          <a:ext cx="3307080" cy="4039235"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17049,7 +17273,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2260427" cy="1429879"/>
+    <xdr:ext cx="2260427" cy="1475599"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="13" name="文本框 12"/>
@@ -17057,8 +17281,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11436985" y="0"/>
-          <a:ext cx="2259965" cy="1429385"/>
+          <a:off x="12708255" y="0"/>
+          <a:ext cx="2259965" cy="1475105"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17200,7 +17424,7 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4816475" cy="1355090"/>
+    <xdr:ext cx="4816475" cy="1395095"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="17" name="文本框 16"/>
@@ -17208,8 +17432,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8381365" y="3688080"/>
-          <a:ext cx="4816475" cy="1355090"/>
+          <a:off x="9309735" y="3808095"/>
+          <a:ext cx="4816475" cy="1395095"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17507,7 +17731,7 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3256276" cy="474489"/>
+    <xdr:ext cx="3256276" cy="485919"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="18" name="文本框 17"/>
@@ -17515,8 +17739,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11436985" y="1577340"/>
-          <a:ext cx="3255645" cy="474345"/>
+          <a:off x="12708255" y="1628775"/>
+          <a:ext cx="3255645" cy="485775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17692,7 +17916,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5222875" cy="1283970"/>
+    <xdr:ext cx="5222875" cy="1323975"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -17700,8 +17924,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4509770" y="7620"/>
-          <a:ext cx="5222875" cy="1283970"/>
+          <a:off x="5011420" y="7620"/>
+          <a:ext cx="5222875" cy="1323975"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17883,7 +18107,7 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1489831" cy="1621592"/>
+    <xdr:ext cx="1489831" cy="1673027"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
@@ -17891,8 +18115,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8258175" y="1226820"/>
-          <a:ext cx="1489710" cy="1621155"/>
+          <a:off x="9146540" y="1266825"/>
+          <a:ext cx="1489710" cy="1672590"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -18253,7 +18477,7 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>10160</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5457190" cy="1461770"/>
+    <xdr:ext cx="5457190" cy="1507490"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="文本框 3"/>
@@ -18261,8 +18485,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6720840" y="2814320"/>
-          <a:ext cx="5457190" cy="1461770"/>
+          <a:off x="7432040" y="2905760"/>
+          <a:ext cx="5457190" cy="1507490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -18412,7 +18636,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5205730" cy="1570355"/>
+    <xdr:ext cx="5205730" cy="1621790"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="文本框 1"/>
@@ -18420,8 +18644,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3705860" y="9525"/>
-          <a:ext cx="5205730" cy="1570355"/>
+          <a:off x="4117340" y="9525"/>
+          <a:ext cx="5205730" cy="1621790"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -18855,10 +19079,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="23.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="23.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -18890,28 +19114,28 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:U163"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20.3796296296296" customWidth="1"/>
+    <col min="1" max="1" width="20.3833333333333" customWidth="1"/>
     <col min="2" max="2" width="46.25" customWidth="1"/>
     <col min="3" max="3" width="11.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="12.1111111111111" customWidth="1"/>
-    <col min="6" max="6" width="7.44444444444444" customWidth="1"/>
-    <col min="7" max="7" width="5.44444444444444" customWidth="1"/>
-    <col min="8" max="8" width="9.44444444444444" customWidth="1"/>
-    <col min="9" max="9" width="13.8796296296296" customWidth="1"/>
-    <col min="10" max="10" width="9.44444444444444" customWidth="1"/>
-    <col min="11" max="12" width="13.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="12.1083333333333" customWidth="1"/>
+    <col min="6" max="6" width="7.44166666666667" customWidth="1"/>
+    <col min="7" max="7" width="5.44166666666667" customWidth="1"/>
+    <col min="8" max="8" width="9.44166666666667" customWidth="1"/>
+    <col min="9" max="9" width="13.8833333333333" customWidth="1"/>
+    <col min="10" max="10" width="9.44166666666667" customWidth="1"/>
+    <col min="11" max="12" width="13.4416666666667" customWidth="1"/>
     <col min="13" max="13" width="11.3333333333333" customWidth="1"/>
     <col min="14" max="14" width="9.33333333333333" customWidth="1"/>
-    <col min="15" max="15" width="28.8796296296296" customWidth="1"/>
+    <col min="15" max="15" width="28.8833333333333" customWidth="1"/>
     <col min="16" max="16" width="6.25" customWidth="1"/>
-    <col min="17" max="17" width="13.6296296296296" customWidth="1"/>
-    <col min="18" max="19" width="11.6296296296296" customWidth="1"/>
+    <col min="17" max="17" width="13.6333333333333" customWidth="1"/>
+    <col min="18" max="19" width="11.6333333333333" customWidth="1"/>
     <col min="20" max="20" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.6" spans="1:21">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>69</v>
       </c>
@@ -19368,7 +19592,6 @@
     <row r="20" spans="3:21">
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
-      <c r="E20"/>
       <c r="F20" s="12"/>
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
@@ -19409,7 +19632,6 @@
     <row r="22" spans="3:21">
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
-      <c r="E22"/>
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -19430,7 +19652,6 @@
     <row r="23" spans="3:21">
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
-      <c r="E23"/>
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
       <c r="H23" s="12"/>
@@ -19451,7 +19672,6 @@
     <row r="24" spans="3:21">
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
-      <c r="E24"/>
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
@@ -19472,7 +19692,6 @@
     <row r="25" spans="3:21">
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
-      <c r="E25"/>
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
@@ -19493,7 +19712,6 @@
     <row r="26" spans="3:21">
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
-      <c r="E26"/>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
       <c r="H26" s="12"/>
@@ -19514,7 +19732,6 @@
     <row r="27" spans="3:21">
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
-      <c r="E27"/>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
@@ -19535,7 +19752,6 @@
     <row r="28" spans="3:21">
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
-      <c r="E28"/>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
       <c r="H28" s="12"/>
@@ -19556,7 +19772,6 @@
     <row r="29" spans="3:21">
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
-      <c r="E29"/>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
@@ -19577,7 +19792,6 @@
     <row r="30" spans="3:21">
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
-      <c r="E30"/>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
@@ -19598,7 +19812,6 @@
     <row r="31" spans="3:21">
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
-      <c r="E31"/>
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
@@ -19619,7 +19832,6 @@
     <row r="32" spans="3:21">
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
-      <c r="E32"/>
       <c r="F32" s="12"/>
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
@@ -19660,7 +19872,6 @@
     <row r="34" spans="3:21">
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
-      <c r="E34"/>
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
@@ -19681,7 +19892,6 @@
     <row r="35" spans="3:21">
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
-      <c r="E35"/>
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
@@ -19702,7 +19912,6 @@
     <row r="36" spans="3:21">
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
-      <c r="E36"/>
       <c r="F36" s="12"/>
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
@@ -19723,7 +19932,6 @@
     <row r="37" spans="3:21">
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
-      <c r="E37"/>
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
@@ -19744,7 +19952,6 @@
     <row r="38" spans="3:21">
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
-      <c r="E38"/>
       <c r="F38" s="12"/>
       <c r="G38" s="12"/>
       <c r="H38" s="12"/>
@@ -19765,7 +19972,6 @@
     <row r="39" spans="3:21">
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
-      <c r="E39"/>
       <c r="F39" s="12"/>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
@@ -19786,7 +19992,6 @@
     <row r="40" spans="3:21">
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
-      <c r="E40"/>
       <c r="F40" s="12"/>
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
@@ -19807,7 +20012,6 @@
     <row r="41" spans="3:21">
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
-      <c r="E41"/>
       <c r="F41" s="12"/>
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
@@ -19828,7 +20032,6 @@
     <row r="42" spans="3:21">
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
-      <c r="E42"/>
       <c r="F42" s="12"/>
       <c r="G42" s="12"/>
       <c r="H42" s="12"/>
@@ -19849,7 +20052,6 @@
     <row r="43" spans="3:21">
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
-      <c r="E43"/>
       <c r="F43" s="12"/>
       <c r="K43" s="12"/>
       <c r="L43" s="12"/>
@@ -19865,7 +20067,6 @@
     <row r="44" spans="3:21">
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
-      <c r="E44"/>
       <c r="F44" s="12"/>
       <c r="K44" s="12"/>
       <c r="L44" s="12"/>
@@ -19951,14 +20152,10 @@
     <row r="50" spans="2:21">
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
-      <c r="D50"/>
-      <c r="E50"/>
-      <c r="F50"/>
       <c r="K50" s="12"/>
       <c r="L50" s="12"/>
       <c r="M50" s="15"/>
       <c r="N50" s="15"/>
-      <c r="O50"/>
       <c r="P50" s="13"/>
       <c r="Q50" s="13"/>
       <c r="R50" s="13"/>
@@ -19969,14 +20166,10 @@
     <row r="51" spans="2:19">
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
-      <c r="D51"/>
-      <c r="E51"/>
-      <c r="F51"/>
       <c r="K51" s="12"/>
       <c r="L51" s="12"/>
       <c r="M51" s="15"/>
       <c r="N51" s="15"/>
-      <c r="O51"/>
       <c r="P51" s="13"/>
       <c r="Q51" s="13"/>
       <c r="R51" s="13"/>
@@ -19985,14 +20178,10 @@
     <row r="52" spans="2:19">
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52"/>
       <c r="K52" s="12"/>
       <c r="L52" s="12"/>
       <c r="M52" s="15"/>
       <c r="N52" s="15"/>
-      <c r="O52"/>
       <c r="P52" s="13"/>
       <c r="Q52" s="13"/>
       <c r="R52" s="13"/>
@@ -20001,14 +20190,10 @@
     <row r="53" spans="2:19">
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53"/>
       <c r="K53" s="12"/>
       <c r="L53" s="12"/>
       <c r="M53" s="15"/>
       <c r="N53" s="15"/>
-      <c r="O53"/>
       <c r="P53" s="13"/>
       <c r="Q53" s="13"/>
       <c r="R53" s="13"/>
@@ -20017,14 +20202,10 @@
     <row r="54" spans="2:19">
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
       <c r="K54" s="12"/>
       <c r="L54" s="12"/>
       <c r="M54" s="15"/>
       <c r="N54" s="15"/>
-      <c r="O54"/>
       <c r="P54" s="13"/>
       <c r="Q54" s="13"/>
       <c r="R54" s="13"/>
@@ -20033,14 +20214,10 @@
     <row r="55" spans="2:19">
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
       <c r="K55" s="12"/>
       <c r="L55" s="12"/>
       <c r="M55" s="15"/>
       <c r="N55" s="15"/>
-      <c r="O55"/>
       <c r="P55" s="13"/>
       <c r="Q55" s="13"/>
       <c r="R55" s="13"/>
@@ -20049,14 +20226,10 @@
     <row r="56" spans="2:19">
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
-      <c r="D56"/>
-      <c r="E56"/>
-      <c r="F56"/>
       <c r="K56" s="12"/>
       <c r="L56" s="12"/>
       <c r="M56" s="15"/>
       <c r="N56" s="15"/>
-      <c r="O56"/>
       <c r="P56" s="13"/>
       <c r="Q56" s="13"/>
       <c r="R56" s="13"/>
@@ -20065,14 +20238,10 @@
     <row r="57" spans="2:19">
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
-      <c r="D57"/>
-      <c r="E57"/>
-      <c r="F57"/>
       <c r="K57" s="12"/>
       <c r="L57" s="12"/>
       <c r="M57" s="15"/>
       <c r="N57" s="15"/>
-      <c r="O57"/>
       <c r="P57" s="13"/>
       <c r="Q57" s="13"/>
       <c r="R57" s="13"/>
@@ -20081,14 +20250,10 @@
     <row r="58" spans="2:19">
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
-      <c r="D58"/>
-      <c r="E58"/>
-      <c r="F58"/>
       <c r="K58" s="12"/>
       <c r="L58" s="12"/>
       <c r="M58" s="15"/>
       <c r="N58" s="15"/>
-      <c r="O58"/>
       <c r="P58" s="13"/>
       <c r="Q58" s="13"/>
       <c r="R58" s="13"/>
@@ -20097,14 +20262,10 @@
     <row r="59" spans="2:19">
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
-      <c r="D59"/>
-      <c r="E59"/>
-      <c r="F59"/>
       <c r="K59" s="12"/>
       <c r="L59" s="12"/>
       <c r="M59" s="15"/>
       <c r="N59" s="15"/>
-      <c r="O59"/>
       <c r="P59" s="13"/>
       <c r="Q59" s="13"/>
       <c r="R59" s="13"/>
@@ -20113,14 +20274,10 @@
     <row r="60" spans="2:19">
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
-      <c r="D60"/>
-      <c r="E60"/>
-      <c r="F60"/>
       <c r="K60" s="12"/>
       <c r="L60" s="12"/>
       <c r="M60" s="15"/>
       <c r="N60" s="15"/>
-      <c r="O60"/>
       <c r="P60" s="13"/>
       <c r="Q60" s="13"/>
       <c r="R60" s="13"/>
@@ -20129,14 +20286,10 @@
     <row r="61" spans="2:19">
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
-      <c r="D61"/>
-      <c r="E61"/>
-      <c r="F61"/>
       <c r="K61" s="12"/>
       <c r="L61" s="12"/>
       <c r="M61" s="15"/>
       <c r="N61" s="15"/>
-      <c r="O61"/>
       <c r="P61" s="13"/>
       <c r="Q61" s="13"/>
       <c r="R61" s="13"/>
@@ -20145,9 +20298,6 @@
     <row r="62" spans="2:19">
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
       <c r="K62" s="12"/>
       <c r="L62" s="12"/>
       <c r="M62" s="15"/>
@@ -20161,9 +20311,6 @@
     <row r="63" spans="2:20">
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63"/>
       <c r="K63" s="12"/>
       <c r="L63" s="12"/>
       <c r="M63" s="15"/>
@@ -20178,9 +20325,6 @@
     <row r="64" spans="2:20">
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
       <c r="K64" s="12"/>
       <c r="L64" s="12"/>
       <c r="M64" s="15"/>
@@ -20195,9 +20339,6 @@
     <row r="65" spans="2:20">
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
       <c r="K65" s="12"/>
       <c r="L65" s="12"/>
       <c r="M65" s="15"/>
@@ -20212,14 +20353,10 @@
     <row r="66" spans="2:20">
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
       <c r="K66" s="12"/>
       <c r="L66" s="12"/>
       <c r="M66" s="15"/>
       <c r="N66" s="15"/>
-      <c r="O66"/>
       <c r="P66" s="14"/>
       <c r="Q66" s="13"/>
       <c r="R66" s="13"/>
@@ -20229,14 +20366,10 @@
     <row r="67" spans="2:19">
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
-      <c r="D67"/>
-      <c r="E67"/>
-      <c r="F67"/>
       <c r="K67" s="12"/>
       <c r="L67" s="12"/>
       <c r="M67" s="15"/>
       <c r="N67" s="15"/>
-      <c r="O67"/>
       <c r="Q67" s="13"/>
       <c r="R67" s="13"/>
       <c r="S67" s="13"/>
@@ -20244,14 +20377,10 @@
     <row r="68" spans="2:19">
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
-      <c r="D68"/>
-      <c r="E68"/>
-      <c r="F68"/>
       <c r="K68" s="12"/>
       <c r="L68" s="12"/>
       <c r="M68" s="15"/>
       <c r="N68" s="15"/>
-      <c r="O68"/>
       <c r="Q68" s="13"/>
       <c r="R68" s="13"/>
       <c r="S68" s="13"/>
@@ -20259,9 +20388,6 @@
     <row r="69" spans="2:14">
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
-      <c r="D69"/>
-      <c r="E69"/>
-      <c r="F69"/>
       <c r="K69" s="12"/>
       <c r="L69" s="12"/>
       <c r="M69" s="15"/>
@@ -20270,9 +20396,6 @@
     <row r="70" spans="2:14">
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
-      <c r="D70"/>
-      <c r="E70"/>
-      <c r="F70"/>
       <c r="K70" s="12"/>
       <c r="L70" s="12"/>
       <c r="M70" s="15"/>
@@ -20281,9 +20404,6 @@
     <row r="71" spans="2:14">
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
-      <c r="D71"/>
-      <c r="E71"/>
-      <c r="F71"/>
       <c r="K71" s="12"/>
       <c r="L71" s="12"/>
       <c r="M71" s="15"/>
@@ -20292,9 +20412,6 @@
     <row r="72" spans="2:14">
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
-      <c r="D72"/>
-      <c r="E72"/>
-      <c r="F72"/>
       <c r="K72" s="12"/>
       <c r="L72" s="12"/>
       <c r="M72" s="15"/>
@@ -20303,9 +20420,6 @@
     <row r="73" spans="2:14">
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
-      <c r="D73"/>
-      <c r="E73"/>
-      <c r="F73"/>
       <c r="K73" s="12"/>
       <c r="L73" s="12"/>
       <c r="M73" s="15"/>
@@ -20314,9 +20428,6 @@
     <row r="74" spans="2:14">
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
-      <c r="D74"/>
-      <c r="E74"/>
-      <c r="F74"/>
       <c r="K74" s="12"/>
       <c r="L74" s="12"/>
       <c r="M74" s="15"/>
@@ -20325,9 +20436,6 @@
     <row r="75" spans="2:14">
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
-      <c r="D75"/>
-      <c r="E75"/>
-      <c r="F75"/>
       <c r="K75" s="12"/>
       <c r="L75" s="12"/>
       <c r="M75" s="15"/>
@@ -20336,9 +20444,6 @@
     <row r="76" spans="2:14">
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
-      <c r="D76"/>
-      <c r="E76"/>
-      <c r="F76"/>
       <c r="K76" s="12"/>
       <c r="L76" s="12"/>
       <c r="M76" s="15"/>
@@ -20347,9 +20452,6 @@
     <row r="77" spans="2:14">
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
-      <c r="D77"/>
-      <c r="E77"/>
-      <c r="F77"/>
       <c r="K77" s="12"/>
       <c r="L77" s="12"/>
       <c r="M77" s="15"/>
@@ -20358,9 +20460,6 @@
     <row r="78" spans="2:14">
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
       <c r="K78" s="12"/>
       <c r="L78" s="12"/>
       <c r="M78" s="15"/>
@@ -20369,9 +20468,6 @@
     <row r="79" spans="2:14">
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
-      <c r="D79"/>
-      <c r="E79"/>
-      <c r="F79"/>
       <c r="K79" s="12"/>
       <c r="L79" s="12"/>
       <c r="M79" s="15"/>
@@ -20380,9 +20476,6 @@
     <row r="80" spans="2:14">
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
-      <c r="D80"/>
-      <c r="E80"/>
-      <c r="F80"/>
       <c r="K80" s="12"/>
       <c r="L80" s="12"/>
       <c r="M80" s="15"/>
@@ -20391,9 +20484,6 @@
     <row r="81" spans="2:14">
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
-      <c r="D81"/>
-      <c r="E81"/>
-      <c r="F81"/>
       <c r="K81" s="12"/>
       <c r="L81" s="12"/>
       <c r="M81" s="15"/>
@@ -20402,9 +20492,6 @@
     <row r="82" spans="2:14">
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
-      <c r="D82"/>
-      <c r="E82"/>
-      <c r="F82"/>
       <c r="K82" s="12"/>
       <c r="L82" s="12"/>
       <c r="M82" s="15"/>
@@ -20413,9 +20500,6 @@
     <row r="83" spans="2:14">
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
-      <c r="D83"/>
-      <c r="E83"/>
-      <c r="F83"/>
       <c r="K83" s="12"/>
       <c r="L83" s="12"/>
       <c r="M83" s="15"/>
@@ -20424,9 +20508,6 @@
     <row r="84" spans="2:14">
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
-      <c r="D84"/>
-      <c r="E84"/>
-      <c r="F84"/>
       <c r="K84" s="12"/>
       <c r="L84" s="12"/>
       <c r="M84" s="15"/>
@@ -20435,9 +20516,6 @@
     <row r="85" spans="2:14">
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
-      <c r="D85"/>
-      <c r="E85"/>
-      <c r="F85"/>
       <c r="K85" s="12"/>
       <c r="L85" s="12"/>
       <c r="M85" s="15"/>
@@ -20446,9 +20524,6 @@
     <row r="86" spans="2:14">
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
-      <c r="D86"/>
-      <c r="E86"/>
-      <c r="F86"/>
       <c r="K86" s="12"/>
       <c r="L86" s="12"/>
       <c r="M86" s="15"/>
@@ -20457,9 +20532,6 @@
     <row r="87" spans="2:14">
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
-      <c r="D87"/>
-      <c r="E87"/>
-      <c r="F87"/>
       <c r="K87" s="12"/>
       <c r="L87" s="12"/>
       <c r="M87" s="15"/>
@@ -20468,9 +20540,6 @@
     <row r="88" spans="2:14">
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
-      <c r="D88"/>
-      <c r="E88"/>
-      <c r="F88"/>
       <c r="K88" s="12"/>
       <c r="L88" s="12"/>
       <c r="M88" s="15"/>
@@ -20479,9 +20548,6 @@
     <row r="89" spans="2:14">
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
-      <c r="D89"/>
-      <c r="E89"/>
-      <c r="F89"/>
       <c r="K89" s="12"/>
       <c r="L89" s="12"/>
       <c r="M89" s="15"/>
@@ -20490,9 +20556,6 @@
     <row r="90" spans="2:14">
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
-      <c r="D90"/>
-      <c r="E90"/>
-      <c r="F90"/>
       <c r="K90" s="12"/>
       <c r="L90" s="12"/>
       <c r="M90" s="15"/>
@@ -20501,9 +20564,6 @@
     <row r="91" spans="2:14">
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
-      <c r="D91"/>
-      <c r="E91"/>
-      <c r="F91"/>
       <c r="K91" s="12"/>
       <c r="L91" s="12"/>
       <c r="M91" s="15"/>
@@ -20512,9 +20572,6 @@
     <row r="92" spans="2:14">
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
-      <c r="D92"/>
-      <c r="E92"/>
-      <c r="F92"/>
       <c r="K92" s="12"/>
       <c r="L92" s="12"/>
       <c r="M92" s="15"/>
@@ -20523,9 +20580,6 @@
     <row r="93" spans="2:14">
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
-      <c r="D93"/>
-      <c r="E93"/>
-      <c r="F93"/>
       <c r="K93" s="12"/>
       <c r="L93" s="12"/>
       <c r="M93" s="15"/>
@@ -20534,9 +20588,6 @@
     <row r="94" spans="2:14">
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
-      <c r="D94"/>
-      <c r="E94"/>
-      <c r="F94"/>
       <c r="K94" s="12"/>
       <c r="L94" s="12"/>
       <c r="M94" s="15"/>
@@ -20545,9 +20596,6 @@
     <row r="95" spans="2:14">
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
-      <c r="D95"/>
-      <c r="E95"/>
-      <c r="F95"/>
       <c r="K95" s="12"/>
       <c r="L95" s="12"/>
       <c r="M95" s="15"/>
@@ -20556,9 +20604,6 @@
     <row r="96" spans="2:14">
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
-      <c r="D96"/>
-      <c r="E96"/>
-      <c r="F96"/>
       <c r="K96" s="12"/>
       <c r="L96" s="12"/>
       <c r="M96" s="15"/>
@@ -20567,9 +20612,6 @@
     <row r="97" spans="2:14">
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
-      <c r="D97"/>
-      <c r="E97"/>
-      <c r="F97"/>
       <c r="K97" s="12"/>
       <c r="L97" s="12"/>
       <c r="M97" s="15"/>
@@ -20578,9 +20620,6 @@
     <row r="98" spans="2:14">
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
-      <c r="D98"/>
-      <c r="E98"/>
-      <c r="F98"/>
       <c r="K98" s="12"/>
       <c r="L98" s="12"/>
       <c r="M98" s="15"/>
@@ -20589,9 +20628,6 @@
     <row r="99" spans="2:14">
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
-      <c r="D99"/>
-      <c r="E99"/>
-      <c r="F99"/>
       <c r="K99" s="12"/>
       <c r="L99" s="12"/>
       <c r="M99" s="15"/>
@@ -20600,9 +20636,6 @@
     <row r="100" spans="2:14">
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
-      <c r="D100"/>
-      <c r="E100"/>
-      <c r="F100"/>
       <c r="K100" s="12"/>
       <c r="L100" s="12"/>
       <c r="M100" s="15"/>
@@ -20611,9 +20644,6 @@
     <row r="101" spans="2:14">
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
-      <c r="D101"/>
-      <c r="E101"/>
-      <c r="F101"/>
       <c r="K101" s="12"/>
       <c r="L101" s="12"/>
       <c r="M101" s="15"/>
@@ -20622,9 +20652,6 @@
     <row r="102" spans="2:14">
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
-      <c r="D102"/>
-      <c r="E102"/>
-      <c r="F102"/>
       <c r="K102" s="12"/>
       <c r="L102" s="12"/>
       <c r="M102" s="15"/>
@@ -20633,9 +20660,6 @@
     <row r="103" spans="2:14">
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
-      <c r="D103"/>
-      <c r="E103"/>
-      <c r="F103"/>
       <c r="K103" s="12"/>
       <c r="L103" s="12"/>
       <c r="M103" s="15"/>
@@ -20644,9 +20668,6 @@
     <row r="104" spans="2:14">
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
-      <c r="D104"/>
-      <c r="E104"/>
-      <c r="F104"/>
       <c r="K104" s="12"/>
       <c r="L104" s="12"/>
       <c r="M104" s="15"/>
@@ -20655,9 +20676,6 @@
     <row r="105" spans="2:14">
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
       <c r="K105" s="12"/>
       <c r="L105" s="12"/>
       <c r="M105" s="15"/>
@@ -20666,9 +20684,6 @@
     <row r="106" spans="2:14">
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
-      <c r="D106"/>
-      <c r="E106"/>
-      <c r="F106"/>
       <c r="K106" s="12"/>
       <c r="L106" s="12"/>
       <c r="M106" s="15"/>
@@ -20677,9 +20692,6 @@
     <row r="107" spans="2:14">
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
-      <c r="D107"/>
-      <c r="E107"/>
-      <c r="F107"/>
       <c r="K107" s="12"/>
       <c r="L107" s="12"/>
       <c r="M107" s="15"/>
@@ -20688,9 +20700,6 @@
     <row r="108" spans="2:14">
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
-      <c r="D108"/>
-      <c r="E108"/>
-      <c r="F108"/>
       <c r="K108" s="12"/>
       <c r="L108" s="12"/>
       <c r="M108" s="15"/>
@@ -20699,9 +20708,6 @@
     <row r="109" spans="2:14">
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
-      <c r="D109"/>
-      <c r="E109"/>
-      <c r="F109"/>
       <c r="K109" s="12"/>
       <c r="L109" s="12"/>
       <c r="M109" s="15"/>
@@ -20935,18 +20941,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="9.44444444444444" customWidth="1"/>
-    <col min="3" max="3" width="12.1111111111111" customWidth="1"/>
-    <col min="4" max="4" width="7.44444444444444" customWidth="1"/>
-    <col min="5" max="5" width="5.44444444444444" customWidth="1"/>
-    <col min="6" max="6" width="9.44444444444444" customWidth="1"/>
-    <col min="7" max="7" width="13.8796296296296" customWidth="1"/>
-    <col min="8" max="8" width="9.44444444444444" customWidth="1"/>
-    <col min="9" max="10" width="14.4444444444444" customWidth="1"/>
-    <col min="11" max="11" width="12.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="9.44166666666667" customWidth="1"/>
+    <col min="3" max="3" width="12.1083333333333" customWidth="1"/>
+    <col min="4" max="4" width="7.44166666666667" customWidth="1"/>
+    <col min="5" max="5" width="5.44166666666667" customWidth="1"/>
+    <col min="6" max="6" width="9.44166666666667" customWidth="1"/>
+    <col min="7" max="7" width="13.8833333333333" customWidth="1"/>
+    <col min="8" max="8" width="9.44166666666667" customWidth="1"/>
+    <col min="9" max="10" width="14.4416666666667" customWidth="1"/>
+    <col min="11" max="11" width="12.5583333333333" customWidth="1"/>
     <col min="12" max="12" width="11.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21308,10 +21314,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="14.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="26.212962962963" customWidth="1"/>
+    <col min="1" max="1" width="14.775" customWidth="1"/>
+    <col min="2" max="2" width="26.2166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -21414,10 +21420,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="12.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="12.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -21600,15 +21606,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:J91"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13" style="3" customWidth="1"/>
     <col min="2" max="2" width="24.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9.44444444444444" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.1111111111111" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.44166666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.1083333333333" style="3" customWidth="1"/>
     <col min="5" max="5" width="20" style="3" customWidth="1"/>
-    <col min="6" max="6" width="19.8796296296296" style="3" customWidth="1"/>
-    <col min="7" max="9" width="10.1111111111111" style="3" customWidth="1"/>
+    <col min="6" max="6" width="19.8833333333333" style="3" customWidth="1"/>
+    <col min="7" max="9" width="10.1083333333333" style="3" customWidth="1"/>
     <col min="10" max="11" width="9" style="3" customWidth="1"/>
     <col min="12" max="16384" width="9" style="3"/>
   </cols>
@@ -23526,15 +23532,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:H91"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="11.6296296296296" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.6333333333333" style="3" customWidth="1"/>
     <col min="2" max="2" width="24.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9.44444444444444" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.1111111111111" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.44166666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.1083333333333" style="3" customWidth="1"/>
     <col min="5" max="5" width="20" style="3" customWidth="1"/>
-    <col min="6" max="6" width="19.8796296296296" style="3" customWidth="1"/>
-    <col min="7" max="8" width="10.1111111111111" style="3" customWidth="1"/>
+    <col min="6" max="6" width="19.8833333333333" style="3" customWidth="1"/>
+    <col min="7" max="8" width="10.1083333333333" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -25124,9 +25130,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:A14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="30.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="30.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -25211,9 +25217,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="19.212962962963" customWidth="1"/>
+    <col min="1" max="1" width="19.2166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -25257,16 +25263,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.87962962962963" defaultRowHeight="15.6" outlineLevelRow="7" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.88333333333333" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="14.7777777777778" style="9" customWidth="1"/>
-    <col min="2" max="2" width="20.4444444444444" style="9" customWidth="1"/>
-    <col min="3" max="3" width="16.1111111111111" style="9" customWidth="1"/>
+    <col min="1" max="1" width="14.775" style="9" customWidth="1"/>
+    <col min="2" max="2" width="20.4416666666667" style="9" customWidth="1"/>
+    <col min="3" max="3" width="16.1083333333333" style="9" customWidth="1"/>
     <col min="4" max="4" width="23" style="10" customWidth="1"/>
-    <col min="5" max="5" width="13.8796296296296" style="9" customWidth="1"/>
-    <col min="6" max="6" width="9.44444444444444" style="9" customWidth="1"/>
-    <col min="7" max="8" width="15.212962962963" style="9" customWidth="1"/>
-    <col min="9" max="16384" width="8.87962962962963" style="9"/>
+    <col min="5" max="5" width="13.8833333333333" style="9" customWidth="1"/>
+    <col min="6" max="6" width="9.44166666666667" style="9" customWidth="1"/>
+    <col min="7" max="8" width="15.2166666666667" style="9" customWidth="1"/>
+    <col min="9" max="16384" width="8.88333333333333" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -25411,7 +25417,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -25435,9 +25441,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="15.1083333333333" customWidth="1"/>
     <col min="2" max="2" width="11.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25469,9 +25475,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="8.87962962962963" customWidth="1"/>
+    <col min="1" max="1" width="8.88333333333333" customWidth="1"/>
     <col min="2" max="2" width="38.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25494,7 +25500,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -25518,9 +25524,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
-    <col min="2" max="2" width="54.212962962963" customWidth="1"/>
+    <col min="2" max="2" width="54.2166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -25542,7 +25548,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -25566,9 +25572,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="8.87962962962963" customWidth="1"/>
+    <col min="1" max="1" width="8.88333333333333" customWidth="1"/>
     <col min="2" max="2" width="38.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25591,7 +25597,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -25615,9 +25621,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="8.87962962962963" customWidth="1"/>
+    <col min="1" max="1" width="8.88333333333333" customWidth="1"/>
     <col min="2" max="2" width="38.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25640,7 +25646,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -25664,9 +25670,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
-    <col min="2" max="2" width="54.212962962963" customWidth="1"/>
+    <col min="2" max="2" width="54.2166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -25688,7 +25694,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -25712,10 +25718,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="11.212962962963" customWidth="1"/>
-    <col min="2" max="2" width="24.1296296296296" customWidth="1"/>
+    <col min="1" max="1" width="11.2166666666667" customWidth="1"/>
+    <col min="2" max="2" width="24.1333333333333" customWidth="1"/>
     <col min="3" max="3" width="11.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25812,9 +25818,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="8.87962962962963" customWidth="1"/>
+    <col min="1" max="1" width="8.88333333333333" customWidth="1"/>
     <col min="2" max="2" width="38.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25837,10 +25843,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="6" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="8.87962962962963" customWidth="1"/>
-    <col min="2" max="4" width="12.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="8.88333333333333" customWidth="1"/>
+    <col min="2" max="4" width="12.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25952,13 +25958,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="11.212962962963" customWidth="1"/>
+    <col min="1" max="2" width="11.2166666666667" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="11.6666666666667" customWidth="1"/>
-    <col min="5" max="6" width="13.8796296296296" customWidth="1"/>
-    <col min="7" max="7" width="16.1111111111111" customWidth="1"/>
+    <col min="5" max="6" width="13.8833333333333" customWidth="1"/>
+    <col min="7" max="7" width="16.1083333333333" customWidth="1"/>
     <col min="8" max="8" width="22.6666666666667" customWidth="1"/>
     <col min="9" max="9" width="9.66666666666667" customWidth="1"/>
   </cols>
@@ -26179,12 +26185,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="20.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="25.1111111111111" customWidth="1"/>
-    <col min="4" max="4" width="26.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="20.4416666666667" customWidth="1"/>
+    <col min="3" max="3" width="25.1083333333333" customWidth="1"/>
+    <col min="4" max="4" width="26.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -26282,11 +26288,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="8.87962962962963" customWidth="1"/>
+    <col min="1" max="1" width="8.88333333333333" customWidth="1"/>
     <col min="2" max="2" width="20" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.8796296296296" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.8833333333333" style="3" customWidth="1"/>
     <col min="4" max="4" width="19.3333333333333" style="3" customWidth="1"/>
     <col min="5" max="5" width="20.3333333333333" style="3" customWidth="1"/>
     <col min="6" max="16382" width="9" style="3"/>
@@ -26413,9 +26419,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="13.4444444444444" customWidth="1"/>
+    <col min="1" max="1" width="13.4416666666667" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="4" width="19.6666666666667" style="3" customWidth="1"/>
   </cols>
@@ -26458,13 +26464,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.212962962963" customWidth="1"/>
-    <col min="3" max="3" width="14.212962962963" customWidth="1"/>
-    <col min="5" max="5" width="8.87962962962963" customWidth="1"/>
+    <col min="1" max="1" width="13.2166666666667" customWidth="1"/>
+    <col min="3" max="3" width="14.2166666666667" customWidth="1"/>
+    <col min="5" max="5" width="8.88333333333333" customWidth="1"/>
     <col min="6" max="6" width="10.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="12.7777777777778" customWidth="1"/>
+    <col min="7" max="7" width="12.775" customWidth="1"/>
     <col min="8" max="8" width="11.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
@@ -26799,7 +26805,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -26810,7 +26816,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -26821,9 +26827,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="19.212962962963" customWidth="1"/>
+    <col min="1" max="1" width="19.2166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -26867,7 +26873,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
     <col min="2" max="2" width="11.6666666666667" customWidth="1"/>
@@ -26973,7 +26979,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet40"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -26984,7 +26990,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet41"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -26995,7 +27001,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet42"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -27006,7 +27012,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet43"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -27017,7 +27023,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet44"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -27028,7 +27034,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet45"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -27039,7 +27045,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet46"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -27050,7 +27056,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet47"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -27061,15 +27067,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet48"/>
   <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="11.6296296296296" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.6333333333333" style="3" customWidth="1"/>
     <col min="2" max="2" width="24.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9.44444444444444" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.1111111111111" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.44166666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.1083333333333" style="3" customWidth="1"/>
     <col min="5" max="5" width="20" style="3" customWidth="1"/>
-    <col min="6" max="6" width="19.8796296296296" style="3" customWidth="1"/>
-    <col min="7" max="8" width="10.1111111111111" style="3" customWidth="1"/>
+    <col min="6" max="6" width="19.8833333333333" style="3" customWidth="1"/>
+    <col min="7" max="8" width="10.1083333333333" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -27163,9 +27169,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet49"/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="2" width="19.6296296296296" customWidth="1"/>
+    <col min="1" max="2" width="19.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -27194,7 +27200,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -27334,7 +27340,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet50"/>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -27360,11 +27366,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet51"/>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="23.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="17.1296296296296" customWidth="1"/>
+    <col min="2" max="2" width="23.1083333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -27456,13 +27462,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet52"/>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="6" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="23.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="10.3796296296296" customWidth="1"/>
+    <col min="2" max="2" width="23.1083333333333" customWidth="1"/>
+    <col min="3" max="3" width="10.3833333333333" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
-    <col min="5" max="5" width="9.62962962962963" customWidth="1"/>
+    <col min="5" max="5" width="9.63333333333333" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -27642,10 +27648,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet53"/>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="14.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="26.212962962963" customWidth="1"/>
+    <col min="1" max="1" width="14.775" customWidth="1"/>
+    <col min="2" max="2" width="26.2166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -27666,10 +27672,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet54"/>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="14.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="26.212962962963" customWidth="1"/>
+    <col min="1" max="1" width="14.775" customWidth="1"/>
+    <col min="2" max="2" width="26.2166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -27690,7 +27696,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet55"/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -27719,7 +27725,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet56"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -27730,7 +27736,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet57"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -27741,10 +27747,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet58"/>
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="23.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="23.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -27774,13 +27780,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="15.5555555555556" customWidth="1"/>
-    <col min="3" max="3" width="11.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="13.8796296296296" customWidth="1"/>
-    <col min="5" max="5" width="16.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="15.5583333333333" customWidth="1"/>
+    <col min="3" max="3" width="11.8916666666667" customWidth="1"/>
+    <col min="4" max="4" width="13.8833333333333" customWidth="1"/>
+    <col min="5" max="5" width="16.1083333333333" customWidth="1"/>
     <col min="6" max="6" width="22.6666666666667" customWidth="1"/>
     <col min="7" max="7" width="9.66666666666667" customWidth="1"/>
   </cols>
@@ -28020,10 +28026,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="11.212962962963" customWidth="1"/>
-    <col min="2" max="2" width="13.8796296296296" customWidth="1"/>
+    <col min="1" max="1" width="11.2166666666667" customWidth="1"/>
+    <col min="2" max="2" width="13.8833333333333" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="11.6666666666667" customWidth="1"/>
   </cols>
@@ -28200,12 +28206,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="20.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="25.1111111111111" customWidth="1"/>
-    <col min="4" max="4" width="26.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="20.4416666666667" customWidth="1"/>
+    <col min="3" max="3" width="25.1083333333333" customWidth="1"/>
+    <col min="4" max="4" width="26.4416666666667" customWidth="1"/>
     <col min="5" max="5" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -28298,9 +28304,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="4" width="9.00925925925926" customWidth="1"/>
+    <col min="1" max="4" width="9.00833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
